--- a/CO国試data/CO_questions_2022.xlsx
+++ b/CO国試data/CO_questions_2022.xlsx
@@ -542,15 +542,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -600,7 +600,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>False</t>
@@ -636,15 +635,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -693,7 +692,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
@@ -732,12 +730,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -786,7 +784,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>False</t>
@@ -825,12 +822,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -880,7 +877,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>False</t>
@@ -916,15 +912,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -973,7 +969,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>False</t>
@@ -1012,12 +1007,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>疾患の診断と治療</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1066,7 +1061,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>False</t>
@@ -1102,15 +1096,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1159,7 +1153,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>True</t>
@@ -1198,12 +1191,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>疾患の診断と治療</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -1252,7 +1245,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>False</t>
@@ -1288,15 +1280,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1345,7 +1337,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>False</t>
@@ -1381,15 +1372,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -1438,7 +1429,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>False</t>
@@ -1474,15 +1464,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>3</v>
       </c>
@@ -1531,7 +1521,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>False</t>
@@ -1567,15 +1556,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -1624,7 +1613,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1660,15 +1648,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -1717,7 +1705,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1753,15 +1740,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -1810,7 +1797,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>False</t>
@@ -1846,15 +1832,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>3</v>
       </c>
@@ -1903,7 +1889,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1939,15 +1924,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>3</v>
       </c>
@@ -2037,15 +2022,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -2135,15 +2120,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -2192,7 +2177,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>True</t>
@@ -2228,15 +2212,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>4</v>
       </c>
@@ -2285,7 +2269,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>True</t>
@@ -2321,15 +2304,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>3</v>
       </c>
@@ -2379,7 +2362,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>False</t>
@@ -2418,12 +2400,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -2472,7 +2454,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>True</t>
@@ -2508,15 +2489,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>3</v>
       </c>
@@ -2606,15 +2587,15 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -2663,7 +2644,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>False</t>
@@ -2699,15 +2679,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -2756,7 +2736,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>False</t>
@@ -2792,15 +2771,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -2849,7 +2828,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>False</t>
@@ -2885,15 +2863,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -2942,7 +2920,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>False</t>
@@ -2978,15 +2955,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>3</v>
       </c>
@@ -3035,7 +3012,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>False</t>
@@ -3071,15 +3047,15 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>1</v>
       </c>
@@ -3128,7 +3104,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>False</t>
@@ -3167,12 +3142,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -3221,7 +3196,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>False</t>
@@ -3257,15 +3231,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>3</v>
       </c>
@@ -3314,7 +3288,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>False</t>
@@ -3350,15 +3323,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>4</v>
       </c>
@@ -3448,15 +3421,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>4</v>
       </c>
@@ -3505,7 +3478,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>False</t>
@@ -3541,15 +3513,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>3</v>
       </c>
@@ -3598,7 +3570,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>False</t>
@@ -3634,15 +3605,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -3691,7 +3662,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>False</t>
@@ -3727,15 +3697,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>3</v>
       </c>
@@ -3784,7 +3754,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>False</t>
@@ -3820,15 +3789,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>3</v>
       </c>
@@ -3877,7 +3846,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>False</t>
@@ -3913,15 +3881,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2</v>
       </c>
@@ -3970,7 +3938,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>False</t>
@@ -4006,15 +3973,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4063,7 +4030,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>False</t>
@@ -4099,15 +4065,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>3</v>
       </c>
@@ -4156,7 +4122,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>True</t>
@@ -4192,15 +4157,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -4249,7 +4214,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>False</t>
@@ -4285,15 +4249,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -4342,7 +4306,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>True</t>
@@ -4378,15 +4341,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -4435,7 +4398,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>False</t>
@@ -4471,15 +4433,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>3</v>
       </c>
@@ -4528,7 +4490,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>True</t>
@@ -4564,15 +4525,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -4621,7 +4582,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
           <t>False</t>
@@ -4660,12 +4620,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>2</v>
       </c>
@@ -4714,7 +4674,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>True</t>
@@ -4750,15 +4709,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -4807,7 +4766,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>False</t>
@@ -4843,15 +4801,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>3</v>
       </c>
@@ -4900,7 +4858,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>False</t>
@@ -4936,15 +4893,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>1</v>
       </c>
@@ -4993,7 +4950,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>False</t>
@@ -5029,15 +4985,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>2</v>
       </c>
@@ -5086,7 +5042,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>True</t>
@@ -5122,15 +5077,15 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>3</v>
       </c>
@@ -5179,7 +5134,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>False</t>
@@ -5215,15 +5169,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>2</v>
       </c>
@@ -5272,7 +5226,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>False</t>
@@ -5308,15 +5261,15 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>3</v>
       </c>
@@ -5365,7 +5318,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>True</t>
@@ -5401,15 +5353,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>3</v>
       </c>
@@ -5458,7 +5410,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>False</t>
@@ -5494,15 +5445,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>4</v>
       </c>
@@ -5551,7 +5502,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>True</t>
@@ -5587,15 +5537,15 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>2</v>
       </c>
@@ -5644,7 +5594,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>False</t>
@@ -5680,15 +5629,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -5737,7 +5686,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>False</t>
@@ -5773,15 +5721,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>2</v>
       </c>
@@ -5830,7 +5778,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>False</t>
@@ -5866,15 +5813,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>2</v>
       </c>
@@ -5923,7 +5870,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>False</t>
@@ -5959,15 +5905,15 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>3</v>
       </c>
@@ -6016,7 +5962,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>True</t>
@@ -6052,15 +5997,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>3</v>
       </c>
@@ -6109,7 +6054,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
           <t>True</t>
@@ -6145,15 +6089,15 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>3</v>
       </c>
@@ -6202,7 +6146,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>False</t>
@@ -6238,15 +6181,15 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>2</v>
       </c>
@@ -6295,7 +6238,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
           <t>False</t>
@@ -6331,15 +6273,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>4</v>
       </c>
@@ -6388,7 +6330,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
           <t>True</t>
@@ -6424,15 +6365,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>2</v>
       </c>
@@ -6481,7 +6422,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>False</t>
@@ -6517,15 +6457,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>3</v>
       </c>
@@ -6574,7 +6514,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
           <t>False</t>
@@ -6610,15 +6549,15 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>4</v>
       </c>
@@ -6708,15 +6647,15 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>4</v>
       </c>
@@ -6806,15 +6745,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>3</v>
       </c>
@@ -6864,7 +6803,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
           <t>True</t>
@@ -6900,15 +6838,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>3</v>
       </c>
@@ -6998,15 +6936,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>3</v>
       </c>
@@ -7096,15 +7034,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>4</v>
       </c>
@@ -7194,15 +7132,15 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>3</v>
       </c>
@@ -7292,15 +7230,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>3</v>
       </c>
@@ -7390,15 +7328,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7488,15 +7426,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7546,7 +7484,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
           <t>False</t>
@@ -7582,15 +7519,15 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>2</v>
       </c>
@@ -7639,7 +7576,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>False</t>
@@ -7675,15 +7611,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>3</v>
       </c>
@@ -7732,7 +7668,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>True</t>
@@ -7771,12 +7706,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>1</v>
       </c>
@@ -7825,7 +7760,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
           <t>False</t>
@@ -7864,12 +7798,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>3</v>
       </c>
@@ -7918,7 +7852,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>True</t>
@@ -7954,15 +7887,15 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>3</v>
       </c>
@@ -8011,7 +7944,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>False</t>
@@ -8047,15 +7979,15 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8104,7 +8036,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>True</t>
@@ -8140,15 +8071,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>心身の成長・発達、加齢</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>2</v>
       </c>
@@ -8197,7 +8128,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>False</t>
@@ -8233,15 +8163,15 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>3</v>
       </c>
@@ -8290,7 +8220,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>False</t>
@@ -8329,12 +8258,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>1</v>
       </c>
@@ -8383,7 +8312,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>False</t>
@@ -8419,15 +8347,15 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>3</v>
       </c>
@@ -8476,7 +8404,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
           <t>False</t>
@@ -8512,15 +8439,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8569,7 +8496,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
           <t>False</t>
@@ -8605,15 +8531,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>2</v>
       </c>
@@ -8662,7 +8588,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>False</t>
@@ -8698,15 +8623,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>3</v>
       </c>
@@ -8755,7 +8680,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>False</t>
@@ -8791,15 +8715,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>視能矯正の枠組み</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>2</v>
       </c>
@@ -8848,7 +8772,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>False</t>
@@ -8884,15 +8807,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>視能矯正の枠組み</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>1</v>
       </c>
@@ -8941,7 +8864,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
           <t>False</t>
@@ -8980,12 +8902,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>2</v>
       </c>
@@ -9034,7 +8956,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
           <t>False</t>
@@ -9070,15 +8991,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>2</v>
       </c>
@@ -9127,7 +9048,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
           <t>False</t>
@@ -9163,15 +9083,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>2</v>
       </c>
@@ -9220,7 +9140,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
           <t>False</t>
@@ -9256,15 +9175,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>3</v>
       </c>
@@ -9313,7 +9232,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
           <t>False</t>
@@ -9349,15 +9267,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>4</v>
       </c>
@@ -9408,7 +9326,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
           <t>False</t>
@@ -9444,15 +9361,15 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -9501,7 +9418,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
           <t>True</t>
@@ -9537,15 +9453,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>3</v>
       </c>
@@ -9635,15 +9551,15 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>2</v>
       </c>
@@ -9692,7 +9608,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
           <t>False</t>
@@ -9731,12 +9646,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>2</v>
       </c>
@@ -9785,7 +9700,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
           <t>True</t>
@@ -9821,15 +9735,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>1</v>
       </c>
@@ -9878,7 +9792,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
           <t>False</t>
@@ -9914,15 +9827,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>2</v>
       </c>
@@ -9972,7 +9885,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
           <t>False</t>
@@ -10008,15 +9920,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>2</v>
       </c>
@@ -10065,7 +9977,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
           <t>False</t>
@@ -10101,15 +10012,15 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>3</v>
       </c>
@@ -10158,7 +10069,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
           <t>True</t>
@@ -10194,15 +10104,15 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10292,15 +10202,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10390,15 +10300,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>3</v>
       </c>
@@ -10447,7 +10357,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
           <t>False</t>
@@ -10483,15 +10392,15 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -10540,7 +10449,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
           <t>False</t>
@@ -10576,15 +10484,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>2</v>
       </c>
@@ -10633,7 +10541,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
           <t>False</t>
@@ -10669,15 +10576,15 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>2</v>
       </c>
@@ -10726,7 +10633,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
           <t>False</t>
@@ -10762,15 +10668,15 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>3</v>
       </c>
@@ -10819,7 +10725,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
           <t>False</t>
@@ -10855,15 +10760,15 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
+          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>1</v>
       </c>
@@ -10913,7 +10818,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
           <t>False</t>
@@ -10949,15 +10853,15 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -11006,7 +10910,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
           <t>True</t>
@@ -11042,15 +10945,15 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>1</v>
       </c>
@@ -11099,7 +11002,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
           <t>False</t>
@@ -11135,15 +11037,15 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>2</v>
       </c>
@@ -11192,7 +11094,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
           <t>False</t>
@@ -11228,15 +11129,15 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11285,7 +11186,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
           <t>False</t>
@@ -11321,15 +11221,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>2</v>
       </c>
@@ -11378,7 +11278,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
           <t>False</t>
@@ -11414,15 +11313,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>2</v>
       </c>
@@ -11471,7 +11370,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
           <t>True</t>
@@ -11507,15 +11405,15 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>2</v>
       </c>
@@ -11564,7 +11462,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
           <t>False</t>
@@ -11600,15 +11497,15 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>2</v>
       </c>
@@ -11657,7 +11554,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
           <t>False</t>
@@ -11693,15 +11589,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11750,7 +11646,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
           <t>False</t>
@@ -11786,15 +11681,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>2</v>
       </c>
@@ -11843,7 +11738,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
           <t>False</t>
@@ -11879,15 +11773,15 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>2</v>
       </c>
@@ -11936,7 +11830,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
           <t>False</t>
@@ -11972,15 +11865,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>2</v>
       </c>
@@ -12029,7 +11922,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
           <t>False</t>
@@ -12065,15 +11957,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>2</v>
       </c>
@@ -12122,7 +12014,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
           <t>False</t>
@@ -12158,15 +12049,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>2</v>
       </c>
@@ -12215,7 +12106,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
           <t>False</t>
@@ -12251,15 +12141,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>2</v>
       </c>
@@ -12308,7 +12198,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
           <t>False</t>
@@ -12344,15 +12233,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>3</v>
       </c>
@@ -12401,7 +12290,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
           <t>False</t>
@@ -12437,15 +12325,15 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>3</v>
       </c>
@@ -12494,7 +12382,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
           <t>False</t>
@@ -12530,15 +12417,15 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>4</v>
       </c>
@@ -12588,7 +12475,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
           <t>False</t>
@@ -12624,15 +12510,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>2</v>
       </c>
@@ -12681,7 +12567,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
           <t>False</t>
@@ -12717,15 +12602,15 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>3</v>
       </c>
@@ -12774,7 +12659,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
           <t>False</t>
@@ -12810,15 +12694,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>2</v>
       </c>
@@ -12867,7 +12751,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
           <t>False</t>
@@ -12903,15 +12786,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>3</v>
       </c>
@@ -12960,7 +12843,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
           <t>False</t>
@@ -12996,15 +12878,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>2</v>
       </c>
@@ -13053,7 +12935,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
           <t>False</t>
@@ -13089,15 +12970,15 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13146,7 +13027,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
           <t>False</t>
@@ -13182,15 +13062,15 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>3</v>
       </c>
@@ -13239,7 +13119,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
           <t>True</t>
@@ -13275,15 +13154,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -13332,7 +13211,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
           <t>False</t>
@@ -13368,15 +13246,15 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>4</v>
       </c>
@@ -13425,7 +13303,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
           <t>False</t>
@@ -13461,15 +13338,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>4</v>
       </c>
@@ -13518,7 +13395,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
           <t>False</t>
@@ -13554,15 +13430,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>2</v>
       </c>
@@ -13611,7 +13487,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
           <t>True</t>
@@ -13647,15 +13522,15 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>5</v>
       </c>
@@ -13745,15 +13620,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>4</v>
       </c>
@@ -13843,15 +13718,15 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>3</v>
       </c>
@@ -13941,15 +13816,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>3</v>
       </c>
@@ -14039,15 +13914,15 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>4</v>
       </c>
@@ -14137,15 +14012,15 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>3</v>
       </c>
@@ -14235,15 +14110,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>2</v>
       </c>
@@ -14333,15 +14208,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>5</v>
       </c>
@@ -14390,7 +14265,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
           <t>True</t>
@@ -14426,15 +14300,15 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>3</v>
       </c>
@@ -14524,15 +14398,15 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>3</v>
       </c>

--- a/CO国試data/CO_questions_2022.xlsx
+++ b/CO国試data/CO_questions_2022.xlsx
@@ -542,12 +542,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -912,12 +912,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>疾患の診断と治療</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>疾患の診断と治療</t>
+          <t>脳、神経系疾患</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>疾患の診断と治療</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>疾患の診断と治療</t>
+          <t>脳、神経系疾患</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼外傷</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1924,12 +1924,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2022,12 +2022,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2120,12 +2120,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2489,12 +2489,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2771,12 +2771,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2955,12 +2955,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3139,12 +3139,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3323,12 +3323,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3421,12 +3421,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3513,12 +3513,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3605,12 +3605,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3697,12 +3697,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>眼位と眼球運動</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3881,12 +3881,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3973,12 +3973,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>隅角検査</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4065,12 +4065,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4341,12 +4341,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4433,12 +4433,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼球運動</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4525,12 +4525,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -4617,12 +4617,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -4801,12 +4801,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼瞼</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -4985,12 +4985,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5077,12 +5077,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5261,12 +5261,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -5353,12 +5353,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -5445,12 +5445,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼窩</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -5721,12 +5721,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -5813,12 +5813,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -5905,12 +5905,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>後天眼球運動障害のリハビリ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -5997,12 +5997,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -6273,12 +6273,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -6365,12 +6365,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -6549,12 +6549,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -6745,12 +6745,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -6838,12 +6838,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -6936,12 +6936,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7132,12 +7132,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼窩</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -7230,12 +7230,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>角膜</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -7426,12 +7426,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -7519,12 +7519,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -7611,12 +7611,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -7703,12 +7703,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -7887,12 +7887,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -7979,12 +7979,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -8071,12 +8071,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>心身の成長・発達、加齢</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>心身の成長・発達、加齢</t>
+          <t>加齢、老化</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -8163,7 +8163,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能障害のリハビリテーション</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>健康の指標</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -8347,12 +8347,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -8439,12 +8439,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>斜視</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -8531,12 +8531,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -8623,12 +8623,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -8715,12 +8715,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正の枠組み</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
+          <t>視能矯正の展開</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正の枠組み</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
+          <t>視能矯正の展開</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -8991,12 +8991,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -9083,12 +9083,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -9175,12 +9175,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -9267,12 +9267,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -9361,12 +9361,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -9453,12 +9453,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -9551,12 +9551,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -9643,12 +9643,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -9735,12 +9735,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -9827,12 +9827,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -9920,12 +9920,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -10012,12 +10012,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -10104,12 +10104,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -10202,12 +10202,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼圧検査</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -10484,12 +10484,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -10668,12 +10668,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -10760,12 +10760,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能障害のリハビリテーション</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>視能障害のリハビリテーション</t>
+          <t>ロービジョン</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -10853,12 +10853,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -10945,12 +10945,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -11037,12 +11037,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -11129,12 +11129,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>硝子体</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼外傷</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -11405,12 +11405,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -11497,12 +11497,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -11589,12 +11589,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -11681,12 +11681,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -11773,12 +11773,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -11865,12 +11865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -11957,12 +11957,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>結膜</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -12049,12 +12049,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>基本的知識</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -12233,12 +12233,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>小児視能特性</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -12325,12 +12325,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -12510,12 +12510,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -12602,12 +12602,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -12786,12 +12786,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -12878,12 +12878,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -12970,12 +12970,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -13062,12 +13062,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -13338,12 +13338,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -13430,12 +13430,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -13522,12 +13522,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -13620,12 +13620,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -13718,12 +13718,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -13816,12 +13816,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -13914,12 +13914,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -14012,12 +14012,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -14110,12 +14110,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>結膜</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -14300,12 +14300,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -14398,12 +14398,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>

--- a/CO国試data/CO_questions_2022.xlsx
+++ b/CO国試data/CO_questions_2022.xlsx
@@ -550,7 +550,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -643,7 +642,11 @@
           <t>眼球</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>網膜</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -735,7 +738,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -827,7 +829,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -920,7 +921,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -1012,7 +1012,6 @@
           <t>脳、神経系疾患</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1104,7 +1103,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1196,7 +1194,6 @@
           <t>脳、神経系疾患</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -1288,7 +1285,6 @@
           <t>眼外傷</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1380,7 +1376,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>副交感神経薬</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -1472,7 +1472,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>3</v>
       </c>
@@ -1564,7 +1568,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -1656,7 +1659,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -1748,7 +1755,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -1840,7 +1851,6 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>3</v>
       </c>
@@ -1932,7 +1942,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>3</v>
       </c>
@@ -2030,7 +2039,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -2128,7 +2136,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>定義と正常、異常</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -2220,7 +2232,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>4</v>
       </c>
@@ -2312,7 +2323,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>3</v>
       </c>
@@ -2405,7 +2420,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -2497,7 +2511,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>遠視</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>3</v>
       </c>
@@ -2595,7 +2613,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -2687,7 +2709,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -2779,7 +2800,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -2871,7 +2891,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -2963,7 +2987,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>3</v>
       </c>
@@ -3055,7 +3078,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>1</v>
       </c>
@@ -3147,7 +3169,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -3239,7 +3260,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>3</v>
       </c>
@@ -3331,7 +3356,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>4</v>
       </c>
@@ -3429,7 +3453,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H33" t="n">
         <v>4</v>
       </c>
@@ -3521,7 +3549,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>3</v>
       </c>
@@ -3613,7 +3640,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -3705,7 +3731,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>3</v>
       </c>
@@ -3797,7 +3822,6 @@
           <t>眼位と眼球運動</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>3</v>
       </c>
@@ -3889,7 +3913,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2</v>
       </c>
@@ -3981,7 +4004,6 @@
           <t>隅角検査</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4073,7 +4095,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>3</v>
       </c>
@@ -4165,7 +4186,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -4257,7 +4277,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -4349,7 +4373,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -4441,7 +4464,11 @@
           <t>眼球運動</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>神経筋接合部障害</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>3</v>
       </c>
@@ -4533,7 +4560,6 @@
           <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -4625,7 +4651,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>2</v>
       </c>
@@ -4717,7 +4742,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -4809,7 +4833,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>瞳孔緊張症〈緊張性瞳孔〉</t>
+        </is>
+      </c>
       <c r="H48" t="n">
         <v>3</v>
       </c>
@@ -4901,7 +4929,11 @@
           <t>眼瞼</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>睫毛、眼瞼内反</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>1</v>
       </c>
@@ -4993,7 +5025,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>2</v>
       </c>
@@ -5085,7 +5116,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H51" t="n">
         <v>3</v>
       </c>
@@ -5177,7 +5212,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H52" t="n">
         <v>2</v>
       </c>
@@ -5269,7 +5308,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>A-V型斜視</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>3</v>
       </c>
@@ -5361,7 +5404,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>3</v>
       </c>
@@ -5453,7 +5500,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H55" t="n">
         <v>4</v>
       </c>
@@ -5545,7 +5596,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H56" t="n">
         <v>2</v>
       </c>
@@ -5637,7 +5692,11 @@
           <t>眼窩</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>眼窩吹き抜け骨折</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -5729,7 +5788,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>2</v>
       </c>
@@ -5821,7 +5884,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H59" t="n">
         <v>2</v>
       </c>
@@ -5913,7 +5980,6 @@
           <t>後天眼球運動障害のリハビリ</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>3</v>
       </c>
@@ -6005,7 +6071,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>3</v>
       </c>
@@ -6097,7 +6162,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>3</v>
       </c>
@@ -6189,7 +6253,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H63" t="n">
         <v>2</v>
       </c>
@@ -6281,7 +6349,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>4</v>
       </c>
@@ -6373,7 +6440,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>2</v>
       </c>
@@ -6465,7 +6531,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>微小斜視</t>
+        </is>
+      </c>
       <c r="H66" t="n">
         <v>3</v>
       </c>
@@ -6557,7 +6627,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>上下斜視</t>
+        </is>
+      </c>
       <c r="H67" t="n">
         <v>4</v>
       </c>
@@ -6655,7 +6729,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H68" t="n">
         <v>4</v>
       </c>
@@ -6753,7 +6831,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>3</v>
       </c>
@@ -6846,7 +6923,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H70" t="n">
         <v>3</v>
       </c>
@@ -6944,7 +7025,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>3</v>
       </c>
@@ -7042,7 +7122,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>4</v>
       </c>
@@ -7140,7 +7219,11 @@
           <t>眼窩</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>眼窩吹き抜け骨折</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>3</v>
       </c>
@@ -7238,7 +7321,11 @@
           <t>角膜</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>角膜変性（症）、角膜ジストロフィ</t>
+        </is>
+      </c>
       <c r="H74" t="n">
         <v>3</v>
       </c>
@@ -7336,7 +7423,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>上下斜視</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7434,7 +7525,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7527,7 +7622,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>副交感神経薬</t>
+        </is>
+      </c>
       <c r="H77" t="n">
         <v>2</v>
       </c>
@@ -7619,7 +7718,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>視神経炎</t>
+        </is>
+      </c>
       <c r="H78" t="n">
         <v>3</v>
       </c>
@@ -7711,7 +7814,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>1</v>
       </c>
@@ -7803,7 +7905,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>3</v>
       </c>
@@ -7895,7 +7996,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>3</v>
       </c>
@@ -7987,7 +8087,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8079,7 +8178,6 @@
           <t>加齢、老化</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>2</v>
       </c>
@@ -8171,7 +8269,6 @@
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>3</v>
       </c>
@@ -8263,7 +8360,6 @@
           <t>健康の指標</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>1</v>
       </c>
@@ -8355,7 +8451,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H86" t="n">
         <v>3</v>
       </c>
@@ -8447,7 +8547,6 @@
           <t>斜視</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8539,7 +8638,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H88" t="n">
         <v>2</v>
       </c>
@@ -8631,7 +8734,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>3</v>
       </c>
@@ -8723,7 +8825,6 @@
           <t>視能矯正の展開</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>2</v>
       </c>
@@ -8815,7 +8916,6 @@
           <t>視能矯正の展開</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>1</v>
       </c>
@@ -8907,7 +9007,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>2</v>
       </c>
@@ -8999,7 +9098,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>2</v>
       </c>
@@ -9091,7 +9194,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H94" t="n">
         <v>2</v>
       </c>
@@ -9183,7 +9290,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>乱視</t>
+        </is>
+      </c>
       <c r="H95" t="n">
         <v>3</v>
       </c>
@@ -9275,7 +9386,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H96" t="n">
         <v>4</v>
       </c>
@@ -9369,7 +9484,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -9461,7 +9580,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>3</v>
       </c>
@@ -9559,7 +9677,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>2</v>
       </c>
@@ -9651,7 +9768,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>2</v>
       </c>
@@ -9743,7 +9859,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>視神経炎</t>
+        </is>
+      </c>
       <c r="H101" t="n">
         <v>1</v>
       </c>
@@ -9835,7 +9955,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>2</v>
       </c>
@@ -9928,7 +10047,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>副交感神経薬</t>
+        </is>
+      </c>
       <c r="H103" t="n">
         <v>2</v>
       </c>
@@ -10020,7 +10143,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>3</v>
       </c>
@@ -10112,7 +10234,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10210,7 +10331,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10308,7 +10428,6 @@
           <t>眼圧検査</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>3</v>
       </c>
@@ -10400,7 +10519,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>遠視</t>
+        </is>
+      </c>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -10492,7 +10615,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Schirmer試験</t>
+        </is>
+      </c>
       <c r="H109" t="n">
         <v>2</v>
       </c>
@@ -10584,7 +10711,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H110" t="n">
         <v>2</v>
       </c>
@@ -10676,7 +10807,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>3</v>
       </c>
@@ -10768,7 +10898,6 @@
           <t>ロービジョン</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>1</v>
       </c>
@@ -10861,7 +10990,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -10953,7 +11081,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>1</v>
       </c>
@@ -11045,7 +11172,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>測定法</t>
+        </is>
+      </c>
       <c r="H115" t="n">
         <v>2</v>
       </c>
@@ -11137,7 +11268,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11229,7 +11364,11 @@
           <t>硝子体</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>硝子体出血、混濁、後部硝子体剥離</t>
+        </is>
+      </c>
       <c r="H117" t="n">
         <v>2</v>
       </c>
@@ -11321,7 +11460,6 @@
           <t>眼外傷</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>2</v>
       </c>
@@ -11413,7 +11551,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>2</v>
       </c>
@@ -11505,7 +11642,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>2</v>
       </c>
@@ -11597,7 +11733,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11689,7 +11824,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H122" t="n">
         <v>2</v>
       </c>
@@ -11781,7 +11920,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>白内障</t>
+        </is>
+      </c>
       <c r="H123" t="n">
         <v>2</v>
       </c>
@@ -11873,7 +12016,6 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>2</v>
       </c>
@@ -11965,7 +12107,11 @@
           <t>結膜</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>結膜炎</t>
+        </is>
+      </c>
       <c r="H125" t="n">
         <v>2</v>
       </c>
@@ -12057,7 +12203,11 @@
           <t>基本的知識</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
       <c r="H126" t="n">
         <v>2</v>
       </c>
@@ -12149,7 +12299,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H127" t="n">
         <v>2</v>
       </c>
@@ -12241,7 +12395,6 @@
           <t>小児視能特性</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>3</v>
       </c>
@@ -12333,7 +12486,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>3</v>
       </c>
@@ -12425,7 +12577,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>老視</t>
+        </is>
+      </c>
       <c r="H130" t="n">
         <v>4</v>
       </c>
@@ -12518,7 +12674,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
       <c r="H131" t="n">
         <v>2</v>
       </c>
@@ -12610,7 +12770,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H132" t="n">
         <v>3</v>
       </c>
@@ -12702,7 +12866,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>2</v>
       </c>
@@ -12794,7 +12957,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H134" t="n">
         <v>3</v>
       </c>
@@ -12886,7 +13053,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>2</v>
       </c>
@@ -12978,7 +13144,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13070,7 +13235,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>3</v>
       </c>
@@ -13162,7 +13326,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -13254,7 +13417,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>4</v>
       </c>
@@ -13346,7 +13508,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>4</v>
       </c>
@@ -13438,7 +13599,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>2</v>
       </c>
@@ -13530,7 +13690,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>瞳孔不同</t>
+        </is>
+      </c>
       <c r="H142" t="n">
         <v>5</v>
       </c>
@@ -13628,7 +13792,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H143" t="n">
         <v>4</v>
       </c>
@@ -13726,7 +13894,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ</t>
+        </is>
+      </c>
       <c r="H144" t="n">
         <v>3</v>
       </c>
@@ -13824,7 +13996,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>3</v>
       </c>
@@ -13922,7 +14093,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>4</v>
       </c>
@@ -14020,7 +14190,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H147" t="n">
         <v>3</v>
       </c>
@@ -14118,7 +14292,6 @@
           <t>結膜</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>2</v>
       </c>
@@ -14216,7 +14389,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H149" t="n">
         <v>5</v>
       </c>
@@ -14308,7 +14485,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>3</v>
       </c>
@@ -14406,7 +14582,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>3</v>
       </c>

--- a/CO国試data/CO_questions_2022.xlsx
+++ b/CO国試data/CO_questions_2022.xlsx
@@ -599,10 +599,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S2" t="b">
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -695,10 +693,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S3" t="b">
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -786,10 +782,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S4" t="b">
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -878,10 +872,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S5" t="b">
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -969,10 +961,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S6" t="b">
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1060,10 +1050,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S7" t="b">
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1242,10 +1230,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S9" t="b">
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1333,10 +1319,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S10" t="b">
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1429,10 +1413,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S11" t="b">
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1525,10 +1507,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S12" t="b">
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1616,10 +1596,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S13" t="b">
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1712,10 +1690,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S14" t="b">
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1808,10 +1784,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S15" t="b">
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1899,10 +1873,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S16" t="b">
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1996,10 +1968,8 @@
           <t>2022_co_22_am016.jpg</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S17" t="b">
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2093,10 +2063,8 @@
           <t>2022_co_22_am017.jpg;2022_co_22_am017_2.jpg;2022_co_22_am017_3.jpg;2022_co_22_am017_4.jpg;2022_co_22_am017_5.jpg;2022_co_22_am017_6.jpg</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S18" t="b">
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2377,10 +2345,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S21" t="b">
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2570,10 +2536,8 @@
           <t>2022_co_22_am022.jpg</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S23" t="b">
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2666,10 +2630,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S24" t="b">
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2757,10 +2719,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S25" t="b">
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2848,10 +2808,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S26" t="b">
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2944,10 +2902,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S27" t="b">
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3035,10 +2991,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S28" t="b">
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3126,10 +3080,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S29" t="b">
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3217,10 +3169,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S30" t="b">
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3313,10 +3263,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S31" t="b">
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3410,10 +3358,8 @@
           <t>2022_co_22_am031.jpg</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S32" t="b">
+        <v>0</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3506,10 +3452,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S33" t="b">
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3597,10 +3541,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S34" t="b">
+        <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3688,10 +3630,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S35" t="b">
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3779,10 +3719,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S36" t="b">
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3870,10 +3808,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S37" t="b">
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3961,10 +3897,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S38" t="b">
+        <v>0</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4052,10 +3986,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S39" t="b">
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4234,10 +4166,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S41" t="b">
+        <v>0</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4421,10 +4351,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S43" t="b">
+        <v>0</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4608,10 +4536,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S45" t="b">
+        <v>0</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4790,10 +4716,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S47" t="b">
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4886,10 +4810,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S48" t="b">
+        <v>0</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4982,10 +4904,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S49" t="b">
+        <v>0</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5169,10 +5089,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S51" t="b">
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5265,10 +5183,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S52" t="b">
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5457,10 +5373,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S54" t="b">
+        <v>0</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5649,10 +5563,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S56" t="b">
+        <v>0</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5745,10 +5657,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S57" t="b">
+        <v>0</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5841,10 +5751,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S58" t="b">
+        <v>0</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5937,10 +5845,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S59" t="b">
+        <v>0</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6210,10 +6116,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S62" t="b">
+        <v>0</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6306,10 +6210,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S63" t="b">
+        <v>0</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6488,10 +6390,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S65" t="b">
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6584,10 +6484,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S66" t="b">
+        <v>0</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6686,10 +6584,8 @@
           <t>2022_co_22_am066.jpg</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S67" t="b">
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6788,10 +6684,8 @@
           <t>2022_co_22_am067.jpg</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S68" t="b">
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7079,10 +6973,8 @@
           <t>2022_co_22_am070.jpg</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S71" t="b">
+        <v>0</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7176,10 +7068,8 @@
           <t>2022_co_22_am071.jpg</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S72" t="b">
+        <v>0</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7278,10 +7168,8 @@
           <t>2022_co_22_am072.jpg</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S73" t="b">
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7380,10 +7268,8 @@
           <t>2022_co_22_am073.jpg</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S74" t="b">
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7482,10 +7368,8 @@
           <t>2022_co_22_am074.jpg</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S75" t="b">
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7579,10 +7463,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S76" t="b">
+        <v>0</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7675,10 +7557,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S77" t="b">
+        <v>0</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7862,10 +7742,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S79" t="b">
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8044,10 +7922,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S81" t="b">
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8135,10 +8011,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S82" t="b">
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8226,10 +8100,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S83" t="b">
+        <v>0</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8317,10 +8189,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S84" t="b">
+        <v>0</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8408,10 +8278,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S85" t="b">
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8504,10 +8372,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S86" t="b">
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8595,10 +8461,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S87" t="b">
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8691,10 +8555,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S88" t="b">
+        <v>0</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -8782,10 +8644,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S89" t="b">
+        <v>0</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -8873,10 +8733,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S90" t="b">
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -8964,10 +8822,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S91" t="b">
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9055,10 +8911,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S92" t="b">
+        <v>0</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9151,10 +9005,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S93" t="b">
+        <v>0</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9247,10 +9099,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S94" t="b">
+        <v>0</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9343,10 +9193,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S95" t="b">
+        <v>0</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9441,10 +9289,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S96" t="b">
+        <v>0</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9634,10 +9480,8 @@
           <t>2022_co_22_pm022.jpg;2022_co_22_pm022_2.jpg;2022_co_22_pm022_3.jpg;2022_co_22_pm022_4.jpg;2022_co_22_pm022_5.jpg</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S98" t="b">
+        <v>0</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -9725,10 +9569,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S99" t="b">
+        <v>0</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -9912,10 +9754,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S101" t="b">
+        <v>0</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10004,10 +9844,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S102" t="b">
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10100,10 +9938,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S103" t="b">
+        <v>0</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10288,10 +10124,8 @@
           <t>2022_co_22_pm029.jpg</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S105" t="b">
+        <v>0</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10385,10 +10219,8 @@
           <t>2022_co_22_pm030.jpg</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S106" t="b">
+        <v>0</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10476,10 +10308,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S107" t="b">
+        <v>0</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -10572,10 +10402,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S108" t="b">
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -10668,10 +10496,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S109" t="b">
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10764,10 +10590,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S110" t="b">
+        <v>0</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10855,10 +10679,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S111" t="b">
+        <v>0</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -10947,10 +10769,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S112" t="b">
+        <v>0</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11038,10 +10858,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S113" t="b">
+        <v>0</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11129,10 +10947,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S114" t="b">
+        <v>0</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11225,10 +11041,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S115" t="b">
+        <v>0</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11321,10 +11135,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S116" t="b">
+        <v>0</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11417,10 +11229,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S117" t="b">
+        <v>0</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11599,10 +11409,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S119" t="b">
+        <v>0</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -11690,10 +11498,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S120" t="b">
+        <v>0</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -11781,10 +11587,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S121" t="b">
+        <v>0</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -11877,10 +11681,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S122" t="b">
+        <v>0</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -11973,10 +11775,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S123" t="b">
+        <v>0</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12064,10 +11864,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S124" t="b">
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12160,10 +11958,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S125" t="b">
+        <v>0</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12256,10 +12052,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S126" t="b">
+        <v>0</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -12352,10 +12146,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S127" t="b">
+        <v>0</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -12443,10 +12235,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S128" t="b">
+        <v>0</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -12534,10 +12324,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S129" t="b">
+        <v>0</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -12631,10 +12419,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S130" t="b">
+        <v>0</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -12727,10 +12513,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S131" t="b">
+        <v>0</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -12823,10 +12607,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S132" t="b">
+        <v>0</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -12914,10 +12696,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S133" t="b">
+        <v>0</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13010,10 +12790,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S134" t="b">
+        <v>0</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13101,10 +12879,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S135" t="b">
+        <v>0</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13192,10 +12968,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S136" t="b">
+        <v>0</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13283,10 +13057,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S137" t="b">
+        <v>0</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -13374,10 +13146,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S138" t="b">
+        <v>0</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -13465,10 +13235,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S139" t="b">
+        <v>0</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -13556,10 +13324,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S140" t="b">
+        <v>0</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -13749,10 +13515,8 @@
           <t>2022_co_22_pm066.jpg</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S142" t="b">
+        <v>0</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -13851,10 +13615,8 @@
           <t>2022_co_22_pm067（不備問題採点除外）.jpg</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S143" t="b">
+        <v>0</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -13953,10 +13715,8 @@
           <t>2022_co_22_pm068.jpg</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S144" t="b">
+        <v>0</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14050,10 +13810,8 @@
           <t>2022_co_22_pm069.jpg</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S145" t="b">
+        <v>0</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -14147,10 +13905,8 @@
           <t>2022_co_22_pm070.jpg;2022_co_22_pm070_2.jpg;2022_co_22_pm070_3.jpg;2022_co_22_pm070_4.jpg;2022_co_22_pm070_5.jpg</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S146" t="b">
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14346,10 +14102,8 @@
           <t>2022_co_22_pm072.jpg</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S148" t="b">
+        <v>0</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -14539,10 +14293,8 @@
           <t>2022_co_22_pm074.jpg</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S150" t="b">
+        <v>0</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -14636,10 +14388,8 @@
           <t>2022_co_22_pm075.jpg</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S151" t="b">
+        <v>0</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>

--- a/CO国試data/CO_questions_2022.xlsx
+++ b/CO国試data/CO_questions_2022.xlsx
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1139,10 +1139,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S8" t="b">
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2144,7 +2142,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2157,10 +2155,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S19" t="b">
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2235,7 +2231,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2248,10 +2244,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S20" t="b">
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2421,7 +2415,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2434,10 +2428,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S22" t="b">
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -4062,7 +4054,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4075,10 +4067,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S40" t="b">
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4247,7 +4237,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4260,10 +4250,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S42" t="b">
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4432,7 +4420,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4445,10 +4433,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S44" t="b">
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4612,7 +4598,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4625,10 +4611,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S46" t="b">
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4980,7 +4964,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4993,10 +4977,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S50" t="b">
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5264,7 +5246,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5277,10 +5259,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S53" t="b">
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5454,7 +5434,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5467,10 +5447,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S55" t="b">
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5921,7 +5899,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5934,10 +5912,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S60" t="b">
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6012,7 +5988,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6025,10 +6001,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S61" t="b">
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6286,7 +6260,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6299,10 +6273,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S64" t="b">
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6761,7 +6733,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6774,10 +6746,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S69" t="b">
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6858,7 +6828,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6876,10 +6846,8 @@
           <t>2022_co_22_am069.jpg;2022_co_22_am069_2.jpg;2022_co_22_am069_3.jpg;2022_co_22_am069_4.jpg;2022_co_22_am069_5.jpg</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S70" t="b">
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7638,7 +7606,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7651,10 +7619,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S78" t="b">
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -7818,7 +7784,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7831,10 +7797,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S80" t="b">
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9370,7 +9334,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -9383,10 +9347,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S97" t="b">
+        <v>1</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -9645,7 +9607,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -9658,10 +9620,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S100" t="b">
+        <v>1</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10014,7 +9974,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -10027,10 +9987,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S104" t="b">
+        <v>1</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11305,7 +11263,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -11318,10 +11276,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S118" t="b">
+        <v>1</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13400,7 +13356,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -13413,10 +13369,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S141" t="b">
+        <v>1</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -13597,7 +13551,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>ABCDE</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -13616,7 +13570,7 @@
         </is>
       </c>
       <c r="S143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -13987,7 +13941,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -14005,10 +13959,8 @@
           <t>2022_co_22_pm071.jpg</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S147" t="b">
+        <v>1</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -14183,7 +14135,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -14196,10 +14148,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S149" t="b">
+        <v>1</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
